--- a/BOM_Board2_控制板pcb_2026-09-02.xlsx
+++ b/BOM_Board2_控制板pcb_2026-09-02.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="BOM_Board2_控制板pcb_2026-09-02" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="BOM_Board2_控制板pcb_2026-09-03" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -220,7 +220,7 @@
     <t>SS54</t>
   </si>
   <si>
-    <t>D1,D2</t>
+    <t>D1,D2,D3</t>
   </si>
   <si>
     <t>SMA_L4.3-W2.6-LS5.0-FD</t>
@@ -1318,7 +1318,7 @@
         <v>67</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
         <v>68</v>
